--- a/public/database_produk.xlsx
+++ b/public/database_produk.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pos-radhika\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pos-radhika\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18A3E4D0-6E9D-4D2A-BEC1-3EC5E07AA06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5633058E-0CD5-48D9-848E-A336BC879FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{1679F4BE-2316-49CF-B2C4-93CE2C61F049}"/>
   </bookViews>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Produk</t>
   </si>
@@ -71,7 +60,13 @@
     <t>Serat kelapa murni untuk anggrek</t>
   </si>
   <si>
-    <t>Dagin kelapa pilihan</t>
+    <t>Satuan</t>
+  </si>
+  <si>
+    <t>Kg</t>
+  </si>
+  <si>
+    <t>Daging kelapa pilihan</t>
   </si>
 </sst>
 </file>
@@ -423,14 +418,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE14BF9-9810-4EA2-8A33-BEF9B74990DD}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -438,13 +434,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -452,13 +451,16 @@
         <v>15000</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -466,13 +468,16 @@
         <v>13000</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -480,9 +485,12 @@
         <v>12000</v>
       </c>
       <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
     </row>

--- a/public/database_produk.xlsx
+++ b/public/database_produk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pos-radhika\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5633058E-0CD5-48D9-848E-A336BC879FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBA54CF-BF3B-4D75-8CBF-3CF5489E2E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{1679F4BE-2316-49CF-B2C4-93CE2C61F049}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>Produk</t>
   </si>
@@ -36,15 +36,6 @@
     <t>Stok</t>
   </si>
   <si>
-    <t>Cocofiber</t>
-  </si>
-  <si>
-    <t>Cocomeat</t>
-  </si>
-  <si>
-    <t>Cocopeat</t>
-  </si>
-  <si>
     <t>Habis</t>
   </si>
   <si>
@@ -67,6 +58,18 @@
   </si>
   <si>
     <t>Daging kelapa pilihan</t>
+  </si>
+  <si>
+    <t>Kelapa Cungkil</t>
+  </si>
+  <si>
+    <t>Kopra Asongan</t>
+  </si>
+  <si>
+    <t>Kopra Regular</t>
+  </si>
+  <si>
+    <t>Buah Kelapa</t>
   </si>
 </sst>
 </file>
@@ -418,10 +421,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE14BF9-9810-4EA2-8A33-BEF9B74990DD}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
     <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.36328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -434,64 +437,81 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>11000</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>15000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>12000</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>13000</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>14000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/public/database_produk.xlsx
+++ b/public/database_produk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\pos-radhika\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\skripsi-pos-chatbot\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBA54CF-BF3B-4D75-8CBF-3CF5489E2E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34AEDAC2-8994-4718-872C-7AE59548F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{1679F4BE-2316-49CF-B2C4-93CE2C61F049}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Produk</t>
   </si>
@@ -33,33 +33,15 @@
     <t>Harga</t>
   </si>
   <si>
-    <t>Stok</t>
-  </si>
-  <si>
-    <t>Habis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ada </t>
-  </si>
-  <si>
     <t>Keterangan</t>
   </si>
   <si>
-    <t>Media tanam serabut kelapa padat</t>
-  </si>
-  <si>
-    <t>Serat kelapa murni untuk anggrek</t>
-  </si>
-  <si>
     <t>Satuan</t>
   </si>
   <si>
     <t>Kg</t>
   </si>
   <si>
-    <t>Daging kelapa pilihan</t>
-  </si>
-  <si>
     <t>Kelapa Cungkil</t>
   </si>
   <si>
@@ -70,12 +52,27 @@
   </si>
   <si>
     <t>Buah Kelapa</t>
+  </si>
+  <si>
+    <t>Cocok untuk bahan baku santan industri, minyak kelapa berkualitas tinggi, atau kelapa parut kering.</t>
+  </si>
+  <si>
+    <t>Pilihan ekonomis untuk kebutuhan bahan baku industri minyak kelapa (CNO).</t>
+  </si>
+  <si>
+    <t>Kualitas terbaik untuk hasil rendemen minyak yang maksimal.</t>
+  </si>
+  <si>
+    <t>Kelapa butiran segar, tersedia dalam berbagai ukuran.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="&quot;Rp&quot;#,##0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -105,8 +102,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -421,97 +430,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE14BF9-9810-4EA2-8A33-BEF9B74990DD}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="4" max="4" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.36328125" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>15000</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2">
+        <v>15000</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>15000</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2">
-        <v>11000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B5" s="2">
+        <v>15000</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B3">
-        <v>12000</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4">
-        <v>13000</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5">
-        <v>14000</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
